--- a/datos-referencia/kpis_hoteles.xlsx
+++ b/datos-referencia/kpis_hoteles.xlsx
@@ -854,10 +854,10 @@
         <v>170</v>
       </c>
       <c r="E7">
-        <v>86.40000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="F7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G7">
         <v>165.89</v>
@@ -872,7 +872,7 @@
         <v>17200</v>
       </c>
       <c r="K7">
-        <v>1070400</v>
+        <v>892400</v>
       </c>
       <c r="L7">
         <v>342528</v>
@@ -884,10 +884,10 @@
         <v>29.1</v>
       </c>
       <c r="O7">
-        <v>227995</v>
+        <v>221555</v>
       </c>
       <c r="P7">
-        <v>21.3</v>
+        <v>24.8</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -1244,10 +1244,10 @@
         <v>95</v>
       </c>
       <c r="E13">
-        <v>83.7</v>
+        <v>91.2</v>
       </c>
       <c r="F13">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G13">
         <v>151.5</v>
@@ -1262,7 +1262,7 @@
         <v>9200</v>
       </c>
       <c r="K13">
-        <v>430600</v>
+        <v>698700</v>
       </c>
       <c r="L13">
         <v>129180</v>
@@ -1274,10 +1274,10 @@
         <v>0</v>
       </c>
       <c r="O13">
-        <v>86981</v>
+        <v>180264</v>
       </c>
       <c r="P13">
-        <v>20.2</v>
+        <v>25.8</v>
       </c>
       <c r="Q13">
         <v>2</v>
@@ -1634,10 +1634,10 @@
         <v>42</v>
       </c>
       <c r="E19">
-        <v>94.8</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="F19">
-        <v>315</v>
+        <v>152</v>
       </c>
       <c r="G19">
         <v>298.62</v>
@@ -1652,7 +1652,7 @@
         <v>8400</v>
       </c>
       <c r="K19">
-        <v>410100</v>
+        <v>455200</v>
       </c>
       <c r="L19">
         <v>114828</v>
@@ -1664,10 +1664,10 @@
         <v>28.8</v>
       </c>
       <c r="O19">
-        <v>105806</v>
+        <v>100599</v>
       </c>
       <c r="P19">
-        <v>25.8</v>
+        <v>22.1</v>
       </c>
       <c r="Q19">
         <v>1</v>

--- a/datos-referencia/kpis_hoteles.xlsx
+++ b/datos-referencia/kpis_hoteles.xlsx
@@ -1637,10 +1637,10 @@
         <v>85.09999999999999</v>
       </c>
       <c r="F19">
-        <v>152</v>
+        <v>310</v>
       </c>
       <c r="G19">
-        <v>298.62</v>
+        <v>263.81</v>
       </c>
       <c r="H19">
         <v>358200</v>

--- a/datos-referencia/kpis_hoteles.xlsx
+++ b/datos-referencia/kpis_hoteles.xlsx
@@ -2,11 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -49,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -412,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -428,95 +429,100 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>grupo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>mes</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>habitaciones</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ocupacion_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>adr_eur</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>revpar_eur</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ingresos_rooms</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ingresos_fb</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ingresos_otros</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>total_ingresos</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>coste_ap_eur</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>coste_ar_comisiones</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>food_cost_pct</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>gop_eur</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>gop_pct</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>facturas_ap_pendientes</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>facturas_ar_pendientes</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>alertas_activas</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>estado_oracle</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>out_of_balance_dias</t>
         </is>
@@ -535,209 +541,224 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>calipolis</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>170</v>
       </c>
-      <c r="E2" t="n">
-        <v>44.2</v>
-      </c>
       <c r="F2" t="n">
-        <v>145</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>64.09</v>
+        <v>130</v>
       </c>
       <c r="H2" t="n">
-        <v>327800</v>
+        <v>55.9</v>
       </c>
       <c r="I2" t="n">
-        <v>41200</v>
+        <v>294593</v>
       </c>
       <c r="J2" t="n">
-        <v>8800</v>
+        <v>38297</v>
       </c>
       <c r="K2" t="n">
-        <v>377800</v>
+        <v>7365</v>
       </c>
       <c r="L2" t="n">
-        <v>120896</v>
+        <v>340255</v>
       </c>
       <c r="M2" t="n">
-        <v>15112</v>
+        <v>108882</v>
       </c>
       <c r="N2" t="n">
-        <v>33.8</v>
+        <v>11784</v>
       </c>
       <c r="O2" t="n">
-        <v>57426</v>
+        <v>31</v>
       </c>
       <c r="P2" t="n">
-        <v>15.2</v>
+        <v>69752</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>20.5</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>SIMULACION</t>
         </is>
       </c>
-      <c r="U2" t="n">
-        <v>2</v>
+      <c r="V2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAL01</t>
+          <t>CAL02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hotel Calipolis Sitges</t>
+          <t>Hotel Calipolis Mar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>170</v>
+          <t>calipolis</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>49.1</v>
+        <v>85</v>
       </c>
       <c r="F3" t="n">
-        <v>150</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>73.65000000000001</v>
+        <v>119</v>
       </c>
       <c r="H3" t="n">
-        <v>365800</v>
+        <v>51.17</v>
       </c>
       <c r="I3" t="n">
-        <v>44100</v>
+        <v>134833</v>
       </c>
       <c r="J3" t="n">
-        <v>9200</v>
+        <v>14832</v>
       </c>
       <c r="K3" t="n">
-        <v>419100</v>
+        <v>3371</v>
       </c>
       <c r="L3" t="n">
-        <v>134112</v>
+        <v>153036</v>
       </c>
       <c r="M3" t="n">
-        <v>16764</v>
+        <v>48972</v>
       </c>
       <c r="N3" t="n">
-        <v>33.1</v>
+        <v>5393</v>
       </c>
       <c r="O3" t="n">
-        <v>67056</v>
+        <v>31</v>
       </c>
       <c r="P3" t="n">
-        <v>16</v>
+        <v>29077</v>
       </c>
       <c r="Q3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
-      </c>
-      <c r="T3" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>SIMULACION</t>
         </is>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAL01</t>
+          <t>CAL03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hotel Calipolis Sitges</t>
+          <t>Calipolis Boutique</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>170</v>
+          <t>calipolis</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
       </c>
       <c r="E4" t="n">
-        <v>63.5</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
-        <v>162</v>
+        <v>44.3</v>
       </c>
       <c r="G4" t="n">
-        <v>102.87</v>
+        <v>176</v>
       </c>
       <c r="H4" t="n">
-        <v>505200</v>
+        <v>77.97</v>
       </c>
       <c r="I4" t="n">
-        <v>58400</v>
+        <v>125684</v>
       </c>
       <c r="J4" t="n">
-        <v>11100</v>
+        <v>20109</v>
       </c>
       <c r="K4" t="n">
-        <v>574700</v>
+        <v>3142</v>
       </c>
       <c r="L4" t="n">
-        <v>183904</v>
+        <v>148935</v>
       </c>
       <c r="M4" t="n">
-        <v>22988</v>
+        <v>47659</v>
       </c>
       <c r="N4" t="n">
-        <v>31.8</v>
+        <v>5027</v>
       </c>
       <c r="O4" t="n">
-        <v>99998</v>
+        <v>31</v>
       </c>
       <c r="P4" t="n">
-        <v>17.4</v>
+        <v>35744</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>SIMULACION</t>
         </is>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -754,283 +775,303 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+          <t>calipolis</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>170</v>
       </c>
-      <c r="E5" t="n">
-        <v>73.8</v>
-      </c>
       <c r="F5" t="n">
-        <v>170</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>125.46</v>
+        <v>136</v>
       </c>
       <c r="H5" t="n">
-        <v>674800</v>
+        <v>69.36</v>
       </c>
       <c r="I5" t="n">
-        <v>72500</v>
+        <v>330154</v>
       </c>
       <c r="J5" t="n">
-        <v>13200</v>
+        <v>42920</v>
       </c>
       <c r="K5" t="n">
-        <v>760500</v>
+        <v>8254</v>
       </c>
       <c r="L5" t="n">
-        <v>243360</v>
+        <v>381328</v>
       </c>
       <c r="M5" t="n">
-        <v>30420</v>
+        <v>122025</v>
       </c>
       <c r="N5" t="n">
-        <v>30.5</v>
+        <v>13206</v>
       </c>
       <c r="O5" t="n">
-        <v>142974</v>
+        <v>31</v>
       </c>
       <c r="P5" t="n">
-        <v>18.8</v>
+        <v>78172</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>20.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>SIMULACION</t>
         </is>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAL01</t>
+          <t>CAL02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hotel Calipolis Sitges</t>
+          <t>Hotel Calipolis Mar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>170</v>
+          <t>calipolis</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>80.2</v>
+        <v>85</v>
       </c>
       <c r="F6" t="n">
-        <v>178</v>
+        <v>51</v>
       </c>
       <c r="G6" t="n">
-        <v>142.76</v>
+        <v>125</v>
       </c>
       <c r="H6" t="n">
-        <v>814200</v>
+        <v>63.75</v>
       </c>
       <c r="I6" t="n">
-        <v>82300</v>
+        <v>151725</v>
       </c>
       <c r="J6" t="n">
-        <v>15100</v>
+        <v>16690</v>
       </c>
       <c r="K6" t="n">
-        <v>911600</v>
+        <v>3793</v>
       </c>
       <c r="L6" t="n">
-        <v>291712</v>
+        <v>172208</v>
       </c>
       <c r="M6" t="n">
-        <v>36464</v>
+        <v>55107</v>
       </c>
       <c r="N6" t="n">
-        <v>29.8</v>
+        <v>6069</v>
       </c>
       <c r="O6" t="n">
-        <v>180497</v>
+        <v>31</v>
       </c>
       <c r="P6" t="n">
-        <v>19.8</v>
+        <v>32720</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>SIMULACION</t>
         </is>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAL01</t>
+          <t>CAL03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hotel Calipolis Sitges</t>
+          <t>Calipolis Boutique</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>170</v>
+          <t>calipolis</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>87.40000000000001</v>
+        <v>52</v>
       </c>
       <c r="F7" t="n">
-        <v>195</v>
+        <v>52.5</v>
       </c>
       <c r="G7" t="n">
-        <v>170.43</v>
+        <v>185</v>
       </c>
       <c r="H7" t="n">
-        <v>872700</v>
+        <v>97.12</v>
       </c>
       <c r="I7" t="n">
-        <v>95400</v>
+        <v>141414</v>
       </c>
       <c r="J7" t="n">
-        <v>17200</v>
+        <v>22626</v>
       </c>
       <c r="K7" t="n">
-        <v>985300</v>
+        <v>3535</v>
       </c>
       <c r="L7" t="n">
-        <v>342528</v>
+        <v>167575</v>
       </c>
       <c r="M7" t="n">
-        <v>42816</v>
+        <v>53624</v>
       </c>
       <c r="N7" t="n">
-        <v>29.1</v>
+        <v>5657</v>
       </c>
       <c r="O7" t="n">
-        <v>244354</v>
+        <v>31</v>
       </c>
       <c r="P7" t="n">
-        <v>24.8</v>
+        <v>40218</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>SIMULACION</t>
         </is>
       </c>
-      <c r="U7" t="n">
-        <v>1</v>
+      <c r="V7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CAL02</t>
+          <t>CAL01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hotel Calipolis Mar</t>
+          <t>Hotel Calipolis Sitges</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>95</v>
+          <t>calipolis</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>41.5</v>
+        <v>170</v>
       </c>
       <c r="F8" t="n">
-        <v>132</v>
+        <v>64</v>
       </c>
       <c r="G8" t="n">
-        <v>54.78</v>
+        <v>142</v>
       </c>
       <c r="H8" t="n">
-        <v>131436</v>
+        <v>90.88</v>
       </c>
       <c r="I8" t="n">
-        <v>16764</v>
+        <v>478938</v>
       </c>
       <c r="J8" t="n">
-        <v>4200</v>
+        <v>62262</v>
       </c>
       <c r="K8" t="n">
-        <v>152400</v>
+        <v>11973</v>
       </c>
       <c r="L8" t="n">
-        <v>45720</v>
+        <v>553173</v>
       </c>
       <c r="M8" t="n">
-        <v>7620</v>
+        <v>177015</v>
       </c>
       <c r="N8" t="n">
-        <v>33.5</v>
+        <v>19158</v>
       </c>
       <c r="O8" t="n">
-        <v>21488</v>
+        <v>31</v>
       </c>
       <c r="P8" t="n">
-        <v>14.1</v>
+        <v>113400</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>20.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>SIMULACION</t>
         </is>
       </c>
-      <c r="U8" t="n">
-        <v>1</v>
+      <c r="V8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1046,209 +1087,224 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>95</v>
+          <t>calipolis</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
       </c>
       <c r="E9" t="n">
-        <v>46.2</v>
+        <v>85</v>
       </c>
       <c r="F9" t="n">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="G9" t="n">
-        <v>63.29</v>
+        <v>130</v>
       </c>
       <c r="H9" t="n">
-        <v>147045</v>
+        <v>83.2</v>
       </c>
       <c r="I9" t="n">
-        <v>18755</v>
+        <v>219232</v>
       </c>
       <c r="J9" t="n">
-        <v>4700</v>
+        <v>24116</v>
       </c>
       <c r="K9" t="n">
-        <v>170500</v>
+        <v>5481</v>
       </c>
       <c r="L9" t="n">
-        <v>51150</v>
+        <v>248829</v>
       </c>
       <c r="M9" t="n">
-        <v>8525</v>
+        <v>79625</v>
       </c>
       <c r="N9" t="n">
-        <v>32.8</v>
+        <v>8769</v>
       </c>
       <c r="O9" t="n">
-        <v>25234</v>
+        <v>31</v>
       </c>
       <c r="P9" t="n">
-        <v>14.8</v>
+        <v>47278</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>SIMULACION</t>
         </is>
       </c>
-      <c r="U9" t="n">
-        <v>1</v>
+      <c r="V9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAL02</t>
+          <t>CAL03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hotel Calipolis Mar</t>
+          <t>Calipolis Boutique</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>calipolis</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>95</v>
-      </c>
       <c r="E10" t="n">
-        <v>59.8</v>
+        <v>52</v>
       </c>
       <c r="F10" t="n">
-        <v>150</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>89.7</v>
+        <v>194</v>
       </c>
       <c r="H10" t="n">
-        <v>217857</v>
+        <v>127.85</v>
       </c>
       <c r="I10" t="n">
-        <v>27643</v>
+        <v>206088</v>
       </c>
       <c r="J10" t="n">
-        <v>5800</v>
+        <v>32974</v>
       </c>
       <c r="K10" t="n">
-        <v>251300</v>
+        <v>5152</v>
       </c>
       <c r="L10" t="n">
-        <v>75390</v>
+        <v>244214</v>
       </c>
       <c r="M10" t="n">
-        <v>12565</v>
+        <v>78148</v>
       </c>
       <c r="N10" t="n">
-        <v>32.1</v>
+        <v>8244</v>
       </c>
       <c r="O10" t="n">
-        <v>41464</v>
+        <v>31</v>
       </c>
       <c r="P10" t="n">
-        <v>16.5</v>
+        <v>58611</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>SIMULACION</t>
         </is>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CAL02</t>
+          <t>CAL01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hotel Calipolis Mar</t>
+          <t>Hotel Calipolis Sitges</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>calipolis</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>95</v>
-      </c>
       <c r="E11" t="n">
-        <v>70.09999999999999</v>
+        <v>170</v>
       </c>
       <c r="F11" t="n">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="G11" t="n">
-        <v>112.16</v>
+        <v>150</v>
       </c>
       <c r="H11" t="n">
-        <v>275464</v>
+        <v>111</v>
       </c>
       <c r="I11" t="n">
-        <v>34936</v>
+        <v>566100</v>
       </c>
       <c r="J11" t="n">
-        <v>7200</v>
+        <v>73593</v>
       </c>
       <c r="K11" t="n">
-        <v>317600</v>
+        <v>14152</v>
       </c>
       <c r="L11" t="n">
-        <v>95280</v>
+        <v>653845</v>
       </c>
       <c r="M11" t="n">
-        <v>15880</v>
+        <v>209230</v>
       </c>
       <c r="N11" t="n">
-        <v>31.4</v>
+        <v>22644</v>
       </c>
       <c r="O11" t="n">
-        <v>56850</v>
+        <v>31</v>
       </c>
       <c r="P11" t="n">
-        <v>17.9</v>
+        <v>135346</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>20.7</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>SIMULACION</t>
         </is>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1265,282 +1321,302 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>95</v>
+          <t>calipolis</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
       </c>
       <c r="E12" t="n">
-        <v>76.40000000000001</v>
+        <v>85</v>
       </c>
       <c r="F12" t="n">
-        <v>167</v>
+        <v>74</v>
       </c>
       <c r="G12" t="n">
-        <v>127.59</v>
+        <v>138</v>
       </c>
       <c r="H12" t="n">
-        <v>324671</v>
+        <v>102.12</v>
       </c>
       <c r="I12" t="n">
-        <v>41129</v>
+        <v>260406</v>
       </c>
       <c r="J12" t="n">
-        <v>8100</v>
+        <v>28645</v>
       </c>
       <c r="K12" t="n">
-        <v>373900</v>
+        <v>6510</v>
       </c>
       <c r="L12" t="n">
-        <v>112170</v>
+        <v>295561</v>
       </c>
       <c r="M12" t="n">
-        <v>18695</v>
+        <v>94580</v>
       </c>
       <c r="N12" t="n">
-        <v>30.7</v>
+        <v>10416</v>
       </c>
       <c r="O12" t="n">
-        <v>69919</v>
+        <v>31</v>
       </c>
       <c r="P12" t="n">
-        <v>18.7</v>
+        <v>56748</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>19.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>SIMULACION</t>
         </is>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CAL02</t>
+          <t>CAL03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hotel Calipolis Mar</t>
+          <t>Calipolis Boutique</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>95</v>
+          <t>calipolis</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
       </c>
       <c r="E13" t="n">
-        <v>91.2</v>
+        <v>52</v>
       </c>
       <c r="F13" t="n">
-        <v>185</v>
+        <v>76.2</v>
       </c>
       <c r="G13" t="n">
-        <v>168.72</v>
+        <v>204</v>
       </c>
       <c r="H13" t="n">
-        <v>612643</v>
+        <v>155.45</v>
       </c>
       <c r="I13" t="n">
-        <v>76857</v>
+        <v>242499</v>
       </c>
       <c r="J13" t="n">
-        <v>9200</v>
+        <v>38800</v>
       </c>
       <c r="K13" t="n">
-        <v>698700</v>
+        <v>6062</v>
       </c>
       <c r="L13" t="n">
-        <v>129180</v>
+        <v>287361</v>
       </c>
       <c r="M13" t="n">
-        <v>21530</v>
+        <v>91956</v>
       </c>
       <c r="N13" t="n">
-        <v>30</v>
+        <v>9700</v>
       </c>
       <c r="O13" t="n">
-        <v>180264</v>
+        <v>31</v>
       </c>
       <c r="P13" t="n">
-        <v>25.8</v>
+        <v>70403</v>
       </c>
       <c r="Q13" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="R13" t="n">
         <v>4</v>
       </c>
-      <c r="R13" t="n">
-        <v>2</v>
-      </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>SIMULACION</t>
         </is>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CAL03</t>
+          <t>CAL01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Calipolis Boutique</t>
+          <t>Hotel Calipolis Sitges</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>42</v>
+          <t>calipolis</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
       </c>
       <c r="E14" t="n">
-        <v>51.2</v>
+        <v>170</v>
       </c>
       <c r="F14" t="n">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="G14" t="n">
-        <v>129.02</v>
+        <v>158</v>
       </c>
       <c r="H14" t="n">
-        <v>153100</v>
+        <v>129.56</v>
       </c>
       <c r="I14" t="n">
-        <v>22800</v>
+        <v>682781</v>
       </c>
       <c r="J14" t="n">
-        <v>5100</v>
+        <v>88762</v>
       </c>
       <c r="K14" t="n">
-        <v>181000</v>
+        <v>17070</v>
       </c>
       <c r="L14" t="n">
-        <v>50680</v>
+        <v>788613</v>
       </c>
       <c r="M14" t="n">
-        <v>8145</v>
+        <v>252356</v>
       </c>
       <c r="N14" t="n">
-        <v>32.5</v>
+        <v>27311</v>
       </c>
       <c r="O14" t="n">
-        <v>35838</v>
+        <v>31</v>
       </c>
       <c r="P14" t="n">
-        <v>19.8</v>
+        <v>167186</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>21.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr">
         <is>
           <t>SIMULACION</t>
         </is>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CAL03</t>
+          <t>CAL02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Calipolis Boutique</t>
+          <t>Hotel Calipolis Mar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>42</v>
+          <t>calipolis</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
       </c>
       <c r="E15" t="n">
-        <v>57.4</v>
+        <v>85</v>
       </c>
       <c r="F15" t="n">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="G15" t="n">
-        <v>148.09</v>
+        <v>145</v>
       </c>
       <c r="H15" t="n">
-        <v>175600</v>
+        <v>118.9</v>
       </c>
       <c r="I15" t="n">
-        <v>25200</v>
+        <v>313302</v>
       </c>
       <c r="J15" t="n">
-        <v>5700</v>
+        <v>34463</v>
       </c>
       <c r="K15" t="n">
-        <v>206500</v>
+        <v>7833</v>
       </c>
       <c r="L15" t="n">
-        <v>57820</v>
+        <v>355598</v>
       </c>
       <c r="M15" t="n">
-        <v>9292</v>
+        <v>113791</v>
       </c>
       <c r="N15" t="n">
-        <v>31.8</v>
+        <v>12532</v>
       </c>
       <c r="O15" t="n">
-        <v>42332</v>
+        <v>31</v>
       </c>
       <c r="P15" t="n">
-        <v>20.5</v>
+        <v>69697</v>
       </c>
       <c r="Q15" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="R15" t="n">
         <v>3</v>
       </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
       <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>SIMULACION</t>
         </is>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1557,209 +1633,224 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>42</v>
+          <t>calipolis</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
       </c>
       <c r="E16" t="n">
-        <v>71.8</v>
+        <v>52</v>
       </c>
       <c r="F16" t="n">
-        <v>272</v>
+        <v>84.5</v>
       </c>
       <c r="G16" t="n">
-        <v>195.3</v>
+        <v>215</v>
       </c>
       <c r="H16" t="n">
-        <v>231800</v>
+        <v>181.67</v>
       </c>
       <c r="I16" t="n">
-        <v>30100</v>
+        <v>292860</v>
       </c>
       <c r="J16" t="n">
-        <v>6400</v>
+        <v>46858</v>
       </c>
       <c r="K16" t="n">
-        <v>268300</v>
+        <v>7322</v>
       </c>
       <c r="L16" t="n">
-        <v>75124</v>
+        <v>347040</v>
       </c>
       <c r="M16" t="n">
-        <v>12074</v>
+        <v>111053</v>
       </c>
       <c r="N16" t="n">
-        <v>30.9</v>
+        <v>11714</v>
       </c>
       <c r="O16" t="n">
-        <v>59294</v>
+        <v>31</v>
       </c>
       <c r="P16" t="n">
-        <v>22.1</v>
+        <v>87454</v>
       </c>
       <c r="Q16" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="R16" t="n">
         <v>3</v>
       </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
       <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>SIMULACION</t>
         </is>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CAL03</t>
+          <t>CAL01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Calipolis Boutique</t>
+          <t>Hotel Calipolis Sitges</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>42</v>
+          <t>calipolis</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
       </c>
       <c r="E17" t="n">
-        <v>84.09999999999999</v>
+        <v>170</v>
       </c>
       <c r="F17" t="n">
-        <v>285</v>
+        <v>91</v>
       </c>
       <c r="G17" t="n">
-        <v>239.69</v>
+        <v>177</v>
       </c>
       <c r="H17" t="n">
-        <v>287900</v>
+        <v>161.07</v>
       </c>
       <c r="I17" t="n">
-        <v>35800</v>
+        <v>821457</v>
       </c>
       <c r="J17" t="n">
-        <v>7100</v>
+        <v>106789</v>
       </c>
       <c r="K17" t="n">
-        <v>330800</v>
+        <v>20536</v>
       </c>
       <c r="L17" t="n">
-        <v>92624</v>
+        <v>948782</v>
       </c>
       <c r="M17" t="n">
-        <v>14886</v>
+        <v>303610</v>
       </c>
       <c r="N17" t="n">
-        <v>30.2</v>
+        <v>32858</v>
       </c>
       <c r="O17" t="n">
-        <v>77407</v>
+        <v>28</v>
       </c>
       <c r="P17" t="n">
-        <v>23.4</v>
+        <v>206834</v>
       </c>
       <c r="Q17" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="R17" t="n">
         <v>2</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
       <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>SIMULACION</t>
         </is>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CAL03</t>
+          <t>CAL02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Calipolis Boutique</t>
+          <t>Hotel Calipolis Mar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>42</v>
+          <t>calipolis</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
       </c>
       <c r="E18" t="n">
-        <v>90.3</v>
+        <v>85</v>
       </c>
       <c r="F18" t="n">
-        <v>298</v>
+        <v>91</v>
       </c>
       <c r="G18" t="n">
-        <v>269.09</v>
+        <v>162</v>
       </c>
       <c r="H18" t="n">
-        <v>320400</v>
+        <v>147.42</v>
       </c>
       <c r="I18" t="n">
-        <v>39200</v>
+        <v>375921</v>
       </c>
       <c r="J18" t="n">
-        <v>7800</v>
+        <v>41351</v>
       </c>
       <c r="K18" t="n">
-        <v>367400</v>
+        <v>9398</v>
       </c>
       <c r="L18" t="n">
-        <v>102872</v>
+        <v>426670</v>
       </c>
       <c r="M18" t="n">
-        <v>16533</v>
+        <v>136534</v>
       </c>
       <c r="N18" t="n">
-        <v>29.5</v>
+        <v>15037</v>
       </c>
       <c r="O18" t="n">
-        <v>88911</v>
+        <v>28</v>
       </c>
       <c r="P18" t="n">
-        <v>24.2</v>
+        <v>85761</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>20.1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t>SIMULACION</t>
         </is>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1776,67 +1867,72 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>calipolis</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>42</v>
-      </c>
       <c r="E19" t="n">
-        <v>85.09999999999999</v>
+        <v>52</v>
       </c>
       <c r="F19" t="n">
-        <v>310</v>
+        <v>93.7</v>
       </c>
       <c r="G19" t="n">
-        <v>263.81</v>
+        <v>241</v>
       </c>
       <c r="H19" t="n">
-        <v>426700</v>
+        <v>225.82</v>
       </c>
       <c r="I19" t="n">
-        <v>43500</v>
+        <v>352275</v>
       </c>
       <c r="J19" t="n">
-        <v>8400</v>
+        <v>56364</v>
       </c>
       <c r="K19" t="n">
-        <v>478600</v>
+        <v>8807</v>
       </c>
       <c r="L19" t="n">
-        <v>114828</v>
+        <v>417446</v>
       </c>
       <c r="M19" t="n">
-        <v>18454</v>
+        <v>133583</v>
       </c>
       <c r="N19" t="n">
-        <v>28.8</v>
+        <v>14091</v>
       </c>
       <c r="O19" t="n">
-        <v>105771</v>
+        <v>28</v>
       </c>
       <c r="P19" t="n">
-        <v>22.1</v>
+        <v>108119</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>25.9</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="inlineStr">
         <is>
           <t>SIMULACION</t>
         </is>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/datos-referencia/kpis_hoteles.xlsx
+++ b/datos-referencia/kpis_hoteles.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>hotel_id</t>
   </si>
@@ -23,6 +23,12 @@
   </si>
   <si>
     <t>grupo</t>
+  </si>
+  <si>
+    <t>ciudad</t>
+  </si>
+  <si>
+    <t>categoria</t>
   </si>
   <si>
     <t>mes</t>
@@ -437,10 +443,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -506,6 +512,12 @@
       </c>
       <c r="V1" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
